--- a/descriptives.xlsx
+++ b/descriptives.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erinbuchanan/GitHub/Research/2_projects/big_team_size/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6128DE-735B-F24B-B2EE-6048C8BEDBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280F6825-B9FB-D04B-B8FE-5F16CA0EE03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" xr2:uid="{00C03AC1-0943-7840-9052-5B04392AF084}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="41">
   <si>
     <t>model</t>
   </si>
@@ -152,6 +152,12 @@
   </si>
   <si>
     <t>row</t>
+  </si>
+  <si>
+    <t>hyp1b_CitationCount</t>
+  </si>
+  <si>
+    <t>hyp1b_Citation5y</t>
   </si>
 </sst>
 </file>
@@ -512,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C587EF64-7959-044E-AF1F-872EDEA94A37}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -552,25 +558,25 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>4.0903729999999996</v>
+        <v>3.6067269999999998</v>
       </c>
       <c r="E2">
-        <v>4.2011070000000004</v>
+        <v>2.4114200000000001</v>
       </c>
       <c r="F2">
-        <v>509</v>
+        <v>34490</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2">
         <v>2</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -581,25 +587,25 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D3">
-        <v>17.256578999999999</v>
+        <v>6.7535220000000002</v>
       </c>
       <c r="E3">
-        <v>178.472195</v>
+        <v>6.63157</v>
       </c>
       <c r="F3">
-        <v>152</v>
+        <v>27114</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -610,25 +616,25 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D4">
-        <v>10.449673000000001</v>
+        <v>4.9265319999999999</v>
       </c>
       <c r="E4">
-        <v>110.41214600000001</v>
+        <v>2.7785850000000001</v>
       </c>
       <c r="F4">
-        <v>765</v>
+        <v>63361</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>3</v>
       </c>
       <c r="I4">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -639,25 +645,25 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D5">
-        <v>6.7867100000000002</v>
+        <v>2.6452830000000001</v>
       </c>
       <c r="E5">
-        <v>4.4524860000000004</v>
+        <v>2.495447</v>
       </c>
       <c r="F5">
-        <v>933</v>
+        <v>10865</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -668,22 +674,22 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D6">
-        <v>4.8490099999999998</v>
+        <v>8.5193739999999991</v>
       </c>
       <c r="E6">
-        <v>3.7601110000000002</v>
+        <v>82.957976000000002</v>
       </c>
       <c r="F6">
-        <v>404</v>
+        <v>73192</v>
       </c>
       <c r="G6">
         <v>4</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>6</v>
@@ -697,25 +703,25 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>4.8064520000000002</v>
+        <v>3.6005479999999999</v>
       </c>
       <c r="E7">
-        <v>2.3210959999999998</v>
+        <v>3.6876790000000002</v>
       </c>
       <c r="F7">
-        <v>248</v>
+        <v>18961</v>
       </c>
       <c r="G7">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
         <v>4</v>
-      </c>
-      <c r="H7">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -726,16 +732,16 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D8">
-        <v>10.90099</v>
+        <v>4.9107969999999996</v>
       </c>
       <c r="E8">
-        <v>135.710645</v>
+        <v>3.3931100000000001</v>
       </c>
       <c r="F8">
-        <v>505</v>
+        <v>6289</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -755,25 +761,25 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D9">
-        <v>4.6635289999999996</v>
+        <v>6.5388869999999999</v>
       </c>
       <c r="E9">
-        <v>2.4862280000000001</v>
+        <v>11.887155</v>
       </c>
       <c r="F9">
-        <v>425</v>
+        <v>113239</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>3</v>
       </c>
       <c r="I9">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
@@ -784,25 +790,25 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D10">
-        <v>34.058441999999999</v>
+        <v>5.699891</v>
       </c>
       <c r="E10">
-        <v>239.83036899999999</v>
+        <v>4.8215029999999999</v>
       </c>
       <c r="F10">
-        <v>462</v>
+        <v>25704</v>
       </c>
       <c r="G10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
@@ -813,16 +819,16 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D11">
-        <v>5.32</v>
+        <v>5.5084949999999999</v>
       </c>
       <c r="E11">
-        <v>2.9962339999999998</v>
+        <v>4.337002</v>
       </c>
       <c r="F11">
-        <v>125</v>
+        <v>4179</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -842,25 +848,25 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D12">
-        <v>4.640288</v>
+        <v>4.4423060000000003</v>
       </c>
       <c r="E12">
-        <v>2.3125589999999998</v>
+        <v>23.039158</v>
       </c>
       <c r="F12">
-        <v>139</v>
+        <v>74704</v>
       </c>
       <c r="G12">
         <v>4</v>
       </c>
       <c r="H12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -871,25 +877,25 @@
         <v>5</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D13">
-        <v>5.3398060000000003</v>
+        <v>6.0047230000000003</v>
       </c>
       <c r="E13">
-        <v>9.1912509999999994</v>
+        <v>5.4299739999999996</v>
       </c>
       <c r="F13">
-        <v>206</v>
+        <v>21809</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -900,25 +906,25 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>4.4531840000000003</v>
+        <v>7.0812549999999996</v>
       </c>
       <c r="E14">
-        <v>2.6187330000000002</v>
+        <v>13.683733</v>
       </c>
       <c r="F14">
-        <v>267</v>
+        <v>148298</v>
       </c>
       <c r="G14">
+        <v>6</v>
+      </c>
+      <c r="H14">
         <v>4</v>
       </c>
-      <c r="H14">
-        <v>3</v>
-      </c>
       <c r="I14">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -929,16 +935,16 @@
         <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15">
-        <v>2.8162389999999999</v>
+        <v>2.498847</v>
       </c>
       <c r="E15">
-        <v>1.9817819999999999</v>
+        <v>1.6476679999999999</v>
       </c>
       <c r="F15">
-        <v>234</v>
+        <v>8676</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -958,25 +964,25 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>24.628378000000001</v>
+        <v>4.6565859999999999</v>
       </c>
       <c r="E16">
-        <v>216.99155999999999</v>
+        <v>63.468803000000001</v>
       </c>
       <c r="F16">
-        <v>148</v>
+        <v>24303</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -987,16 +993,16 @@
         <v>5</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>6.6145250000000004</v>
+        <v>8.2463060000000006</v>
       </c>
       <c r="E17">
-        <v>3.4170769999999999</v>
+        <v>25.401119999999999</v>
       </c>
       <c r="F17">
-        <v>179</v>
+        <v>21928</v>
       </c>
       <c r="G17">
         <v>6</v>
@@ -1005,7 +1011,7 @@
         <v>4</v>
       </c>
       <c r="I17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -1016,25 +1022,25 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D18">
-        <v>3.5404260000000001</v>
+        <v>4.6515370000000003</v>
       </c>
       <c r="E18">
-        <v>1.840157</v>
+        <v>4.559793</v>
       </c>
       <c r="F18">
-        <v>235</v>
+        <v>40782</v>
       </c>
       <c r="G18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -1045,16 +1051,16 @@
         <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D19">
-        <v>3.6259540000000001</v>
+        <v>2.841107</v>
       </c>
       <c r="E19">
-        <v>2.2882169999999999</v>
+        <v>2.1271080000000002</v>
       </c>
       <c r="F19">
-        <v>131</v>
+        <v>5639</v>
       </c>
       <c r="G19">
         <v>3</v>
@@ -1063,7 +1069,7 @@
         <v>2</v>
       </c>
       <c r="I19">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
@@ -1074,25 +1080,25 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D20">
-        <v>2.9452050000000001</v>
+        <v>5.0129219999999997</v>
       </c>
       <c r="E20">
-        <v>2.4374989999999999</v>
+        <v>4.6776819999999999</v>
       </c>
       <c r="F20">
-        <v>73</v>
+        <v>58118</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
@@ -1103,16 +1109,16 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D21">
-        <v>4.3684209999999997</v>
+        <v>4.655157</v>
       </c>
       <c r="E21">
-        <v>2.0333480000000002</v>
+        <v>2.819423</v>
       </c>
       <c r="F21">
-        <v>19</v>
+        <v>18188</v>
       </c>
       <c r="G21">
         <v>4</v>
@@ -1132,25 +1138,25 @@
         <v>5</v>
       </c>
       <c r="C22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22">
+        <v>5.3886229999999999</v>
+      </c>
+      <c r="E22">
+        <v>5.3220010000000002</v>
+      </c>
+      <c r="F22">
+        <v>8157</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22">
+        <v>3</v>
+      </c>
+      <c r="I22">
         <v>7</v>
-      </c>
-      <c r="D22">
-        <v>5.8598730000000003</v>
-      </c>
-      <c r="E22">
-        <v>3.8036059999999998</v>
-      </c>
-      <c r="F22">
-        <v>157</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-      <c r="H22">
-        <v>3</v>
-      </c>
-      <c r="I22">
-        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
@@ -1161,22 +1167,22 @@
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D23">
-        <v>4.6511630000000004</v>
+        <v>5.0092169999999996</v>
       </c>
       <c r="E23">
-        <v>3.5381170000000002</v>
+        <v>2.73529</v>
       </c>
       <c r="F23">
-        <v>43</v>
+        <v>37864</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I23">
         <v>6</v>
@@ -1190,25 +1196,25 @@
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D24">
-        <v>2.694118</v>
+        <v>2.7439800000000001</v>
       </c>
       <c r="E24">
-        <v>1.165205</v>
+        <v>2.5563159999999998</v>
       </c>
       <c r="F24">
-        <v>85</v>
+        <v>34677</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
@@ -1219,25 +1225,25 @@
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D25">
-        <v>5.75</v>
+        <v>5.4214869999999999</v>
       </c>
       <c r="E25">
-        <v>3.7299850000000001</v>
+        <v>11.740494999999999</v>
       </c>
       <c r="F25">
-        <v>44</v>
+        <v>31982</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
@@ -1248,25 +1254,25 @@
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D26">
-        <v>5.1142859999999999</v>
+        <v>2.5194809999999999</v>
       </c>
       <c r="E26">
-        <v>2.7522340000000001</v>
+        <v>1.4291180000000001</v>
       </c>
       <c r="F26">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
@@ -1277,25 +1283,25 @@
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D27">
-        <v>2.65</v>
+        <v>5.0643440000000002</v>
       </c>
       <c r="E27">
-        <v>1.4823820000000001</v>
+        <v>11.671177999999999</v>
       </c>
       <c r="F27">
-        <v>60</v>
+        <v>77350</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
@@ -1306,25 +1312,25 @@
         <v>5</v>
       </c>
       <c r="C28" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D28">
-        <v>2.6388889999999998</v>
+        <v>4.5634290000000002</v>
       </c>
       <c r="E28">
-        <v>1.3554710000000001</v>
+        <v>2.5453809999999999</v>
       </c>
       <c r="F28">
-        <v>36</v>
+        <v>3161</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
@@ -1335,25 +1341,1649 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
+        <v>22</v>
+      </c>
+      <c r="D29">
+        <v>2.61605</v>
+      </c>
+      <c r="E29">
+        <v>2.4727890000000001</v>
+      </c>
+      <c r="F29">
+        <v>13869</v>
+      </c>
+      <c r="G29">
+        <v>2</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30">
+        <v>183.203914</v>
+      </c>
+      <c r="E30">
+        <v>970.00488800000005</v>
+      </c>
+      <c r="F30">
+        <v>34490</v>
+      </c>
+      <c r="G30">
+        <v>18</v>
+      </c>
+      <c r="H30">
+        <v>3</v>
+      </c>
+      <c r="I30">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D31">
+        <v>123.999262</v>
+      </c>
+      <c r="E31">
+        <v>536.55038300000001</v>
+      </c>
+      <c r="F31">
+        <v>27114</v>
+      </c>
+      <c r="G31">
+        <v>39</v>
+      </c>
+      <c r="H31">
+        <v>11</v>
+      </c>
+      <c r="I31">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32">
+        <v>98.470921000000004</v>
+      </c>
+      <c r="E32">
+        <v>476.151385</v>
+      </c>
+      <c r="F32">
+        <v>63361</v>
+      </c>
+      <c r="G32">
+        <v>26</v>
+      </c>
+      <c r="H32">
+        <v>7</v>
+      </c>
+      <c r="I32">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" t="s">
+        <v>27</v>
+      </c>
+      <c r="D33">
+        <v>124.805983</v>
+      </c>
+      <c r="E33">
+        <v>501.35212100000001</v>
+      </c>
+      <c r="F33">
+        <v>10865</v>
+      </c>
+      <c r="G33">
+        <v>23</v>
+      </c>
+      <c r="H33">
+        <v>5</v>
+      </c>
+      <c r="I33">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34">
+        <v>147.301399</v>
+      </c>
+      <c r="E34">
+        <v>928.46455500000002</v>
+      </c>
+      <c r="F34">
+        <v>73192</v>
+      </c>
+      <c r="G34">
+        <v>30</v>
+      </c>
+      <c r="H34">
+        <v>9</v>
+      </c>
+      <c r="I34">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="B35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" t="s">
+        <v>26</v>
+      </c>
+      <c r="D35">
+        <v>216.28453099999999</v>
+      </c>
+      <c r="E35">
+        <v>958.41467899999998</v>
+      </c>
+      <c r="F35">
+        <v>18961</v>
+      </c>
+      <c r="G35">
+        <v>44</v>
+      </c>
+      <c r="H35">
+        <v>10</v>
+      </c>
+      <c r="I35">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
+      <c r="B36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36">
+        <v>86.727142999999998</v>
+      </c>
+      <c r="E36">
+        <v>374.13895200000002</v>
+      </c>
+      <c r="F36">
+        <v>6289</v>
+      </c>
+      <c r="G36">
+        <v>22</v>
+      </c>
+      <c r="H36">
+        <v>5</v>
+      </c>
+      <c r="I36">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37">
+        <v>156.48267799999999</v>
+      </c>
+      <c r="E37">
+        <v>1007.195669</v>
+      </c>
+      <c r="F37">
+        <v>113239</v>
+      </c>
+      <c r="G37">
+        <v>43</v>
+      </c>
+      <c r="H37">
+        <v>13</v>
+      </c>
+      <c r="I37">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38">
+        <v>136.964325</v>
+      </c>
+      <c r="E38">
+        <v>610.509772</v>
+      </c>
+      <c r="F38">
+        <v>25704</v>
+      </c>
+      <c r="G38">
+        <v>43</v>
+      </c>
+      <c r="H38">
+        <v>13</v>
+      </c>
+      <c r="I38">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>39</v>
+      </c>
+      <c r="C39" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39">
+        <v>35.040680000000002</v>
+      </c>
+      <c r="E39">
+        <v>66.775881999999996</v>
+      </c>
+      <c r="F39">
+        <v>4179</v>
+      </c>
+      <c r="G39">
+        <v>15</v>
+      </c>
+      <c r="H39">
+        <v>4</v>
+      </c>
+      <c r="I39">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40">
+        <v>107.855068</v>
+      </c>
+      <c r="E40">
+        <v>489.25554699999998</v>
+      </c>
+      <c r="F40">
+        <v>74704</v>
+      </c>
+      <c r="G40">
+        <v>22</v>
+      </c>
+      <c r="H40">
+        <v>5</v>
+      </c>
+      <c r="I40">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" t="s">
+        <v>18</v>
+      </c>
+      <c r="D41">
+        <v>66.968773999999996</v>
+      </c>
+      <c r="E41">
+        <v>268.11964</v>
+      </c>
+      <c r="F41">
+        <v>21809</v>
+      </c>
+      <c r="G41">
+        <v>25</v>
+      </c>
+      <c r="H41">
+        <v>7</v>
+      </c>
+      <c r="I41">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C42" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42">
+        <v>134.96697900000001</v>
+      </c>
+      <c r="E42">
+        <v>545.86022800000001</v>
+      </c>
+      <c r="F42">
+        <v>148298</v>
+      </c>
+      <c r="G42">
+        <v>35</v>
+      </c>
+      <c r="H42">
+        <v>9</v>
+      </c>
+      <c r="I42">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43">
+        <v>211.954126</v>
+      </c>
+      <c r="E43">
+        <v>894.31874300000004</v>
+      </c>
+      <c r="F43">
+        <v>8676</v>
+      </c>
+      <c r="G43">
+        <v>37</v>
+      </c>
+      <c r="H43">
+        <v>7</v>
+      </c>
+      <c r="I43">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44">
+        <v>198.74097800000001</v>
+      </c>
+      <c r="E44">
+        <v>1061.084294</v>
+      </c>
+      <c r="F44">
+        <v>24303</v>
+      </c>
+      <c r="G44">
+        <v>21</v>
+      </c>
+      <c r="H44">
+        <v>5</v>
+      </c>
+      <c r="I44">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45">
+        <v>399.998358</v>
+      </c>
+      <c r="E45">
+        <v>1776.152417</v>
+      </c>
+      <c r="F45">
+        <v>21928</v>
+      </c>
+      <c r="G45">
+        <v>86</v>
+      </c>
+      <c r="H45">
+        <v>16</v>
+      </c>
+      <c r="I45">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46">
+        <v>90.011082999999999</v>
+      </c>
+      <c r="E46">
+        <v>312.078216</v>
+      </c>
+      <c r="F46">
+        <v>40782</v>
+      </c>
+      <c r="G46">
+        <v>26</v>
+      </c>
+      <c r="H46">
+        <v>7</v>
+      </c>
+      <c r="I46">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47">
+        <v>249.31211200000001</v>
+      </c>
+      <c r="E47">
+        <v>1143.077288</v>
+      </c>
+      <c r="F47">
+        <v>5639</v>
+      </c>
+      <c r="G47">
+        <v>37</v>
+      </c>
+      <c r="H47">
+        <v>8</v>
+      </c>
+      <c r="I47">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48">
+        <v>93.503871000000004</v>
+      </c>
+      <c r="E48">
+        <v>525.98291200000006</v>
+      </c>
+      <c r="F48">
+        <v>58118</v>
+      </c>
+      <c r="G48">
+        <v>26</v>
+      </c>
+      <c r="H48">
+        <v>8</v>
+      </c>
+      <c r="I48">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49">
+        <v>70.882284999999996</v>
+      </c>
+      <c r="E49">
+        <v>178.51736500000001</v>
+      </c>
+      <c r="F49">
+        <v>18188</v>
+      </c>
+      <c r="G49">
+        <v>24</v>
+      </c>
+      <c r="H49">
+        <v>6</v>
+      </c>
+      <c r="I49">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D50">
+        <v>83.744513999999995</v>
+      </c>
+      <c r="E50">
+        <v>275.14543700000002</v>
+      </c>
+      <c r="F50">
+        <v>8157</v>
+      </c>
+      <c r="G50">
+        <v>24</v>
+      </c>
+      <c r="H50">
+        <v>5</v>
+      </c>
+      <c r="I50">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>39</v>
+      </c>
+      <c r="C51" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51">
+        <v>110.466353</v>
+      </c>
+      <c r="E51">
+        <v>354.12328000000002</v>
+      </c>
+      <c r="F51">
+        <v>37864</v>
+      </c>
+      <c r="G51">
+        <v>33</v>
+      </c>
+      <c r="H51">
+        <v>9</v>
+      </c>
+      <c r="I51">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>39</v>
+      </c>
+      <c r="C52" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52">
+        <v>115.358018</v>
+      </c>
+      <c r="E52">
+        <v>586.15899999999999</v>
+      </c>
+      <c r="F52">
+        <v>34677</v>
+      </c>
+      <c r="G52">
+        <v>20</v>
+      </c>
+      <c r="H52">
+        <v>4</v>
+      </c>
+      <c r="I52">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53">
+        <v>120.710212</v>
+      </c>
+      <c r="E53">
+        <v>437.40921300000002</v>
+      </c>
+      <c r="F53">
+        <v>31982</v>
+      </c>
+      <c r="G53">
+        <v>31</v>
+      </c>
+      <c r="H53">
+        <v>9</v>
+      </c>
+      <c r="I53">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" t="s">
+        <v>33</v>
+      </c>
+      <c r="D54">
+        <v>264.688312</v>
+      </c>
+      <c r="E54">
+        <v>1037.5791059999999</v>
+      </c>
+      <c r="F54">
+        <v>77</v>
+      </c>
+      <c r="G54">
+        <v>45</v>
+      </c>
+      <c r="H54">
+        <v>20</v>
+      </c>
+      <c r="I54">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55">
+        <v>121.863788</v>
+      </c>
+      <c r="E55">
+        <v>599.84510799999998</v>
+      </c>
+      <c r="F55">
+        <v>77350</v>
+      </c>
+      <c r="G55">
+        <v>32</v>
+      </c>
+      <c r="H55">
+        <v>10</v>
+      </c>
+      <c r="I55">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56" t="s">
+        <v>28</v>
+      </c>
+      <c r="D56">
+        <v>58.254666</v>
+      </c>
+      <c r="E56">
+        <v>131.072316</v>
+      </c>
+      <c r="F56">
+        <v>3161</v>
+      </c>
+      <c r="G56">
+        <v>24</v>
+      </c>
+      <c r="H56">
+        <v>7</v>
+      </c>
+      <c r="I56">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>39</v>
+      </c>
+      <c r="C57" t="s">
+        <v>22</v>
+      </c>
+      <c r="D57">
+        <v>189.19403</v>
+      </c>
+      <c r="E57">
+        <v>731.07022700000005</v>
+      </c>
+      <c r="F57">
+        <v>13869</v>
+      </c>
+      <c r="G57">
+        <v>35</v>
+      </c>
+      <c r="H57">
+        <v>7</v>
+      </c>
+      <c r="I57">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>40</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58">
+        <v>34.628008000000001</v>
+      </c>
+      <c r="E58">
+        <v>173.28135700000001</v>
+      </c>
+      <c r="F58">
+        <v>34490</v>
+      </c>
+      <c r="G58">
+        <v>10</v>
+      </c>
+      <c r="H58">
+        <v>2</v>
+      </c>
+      <c r="I58">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>40</v>
+      </c>
+      <c r="C59" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59">
+        <v>31.224902</v>
+      </c>
+      <c r="E59">
+        <v>82.817006000000006</v>
+      </c>
+      <c r="F59">
+        <v>63361</v>
+      </c>
+      <c r="G59">
+        <v>13</v>
+      </c>
+      <c r="H59">
+        <v>4</v>
+      </c>
+      <c r="I59">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>40</v>
+      </c>
+      <c r="C60" t="s">
+        <v>25</v>
+      </c>
+      <c r="D60">
+        <v>33.851331000000002</v>
+      </c>
+      <c r="E60">
+        <v>69.572199999999995</v>
+      </c>
+      <c r="F60">
+        <v>27114</v>
+      </c>
+      <c r="G60">
+        <v>16</v>
+      </c>
+      <c r="H60">
+        <v>6</v>
+      </c>
+      <c r="I60">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>40</v>
+      </c>
+      <c r="C61" t="s">
+        <v>27</v>
+      </c>
+      <c r="D61">
+        <v>17.476023999999999</v>
+      </c>
+      <c r="E61">
+        <v>55.337806</v>
+      </c>
+      <c r="F61">
+        <v>10865</v>
+      </c>
+      <c r="G61">
+        <v>7</v>
+      </c>
+      <c r="H61">
+        <v>2</v>
+      </c>
+      <c r="I61">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>40</v>
+      </c>
+      <c r="C62" t="s">
+        <v>26</v>
+      </c>
+      <c r="D62">
+        <v>22.870681999999999</v>
+      </c>
+      <c r="E62">
+        <v>42.484442000000001</v>
+      </c>
+      <c r="F62">
+        <v>18961</v>
+      </c>
+      <c r="G62">
+        <v>12</v>
+      </c>
+      <c r="H62">
+        <v>4</v>
+      </c>
+      <c r="I62">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>40</v>
+      </c>
+      <c r="C63" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63">
+        <v>37.080267999999997</v>
+      </c>
+      <c r="E63">
+        <v>121.010795</v>
+      </c>
+      <c r="F63">
+        <v>73192</v>
+      </c>
+      <c r="G63">
+        <v>14</v>
+      </c>
+      <c r="H63">
+        <v>5</v>
+      </c>
+      <c r="I63">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>40</v>
+      </c>
+      <c r="C64" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64">
+        <v>19.948004000000001</v>
+      </c>
+      <c r="E64">
+        <v>60.078775999999998</v>
+      </c>
+      <c r="F64">
+        <v>6289</v>
+      </c>
+      <c r="G64">
+        <v>9</v>
+      </c>
+      <c r="H64">
+        <v>3</v>
+      </c>
+      <c r="I64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>40</v>
+      </c>
+      <c r="C65" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65">
+        <v>41.202660000000002</v>
+      </c>
+      <c r="E65">
+        <v>157.229309</v>
+      </c>
+      <c r="F65">
+        <v>113239</v>
+      </c>
+      <c r="G65">
+        <v>18</v>
+      </c>
+      <c r="H65">
+        <v>7</v>
+      </c>
+      <c r="I65">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>40</v>
+      </c>
+      <c r="C66" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66">
+        <v>32.321390000000001</v>
+      </c>
+      <c r="E66">
+        <v>58.301454</v>
+      </c>
+      <c r="F66">
+        <v>25704</v>
+      </c>
+      <c r="G66">
+        <v>17</v>
+      </c>
+      <c r="H66">
+        <v>7</v>
+      </c>
+      <c r="I66">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>40</v>
+      </c>
+      <c r="C67" t="s">
+        <v>31</v>
+      </c>
+      <c r="D67">
+        <v>10.340512</v>
+      </c>
+      <c r="E67">
+        <v>17.468295000000001</v>
+      </c>
+      <c r="F67">
+        <v>4179</v>
+      </c>
+      <c r="G67">
+        <v>6</v>
+      </c>
+      <c r="H67">
+        <v>2</v>
+      </c>
+      <c r="I67">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>40</v>
+      </c>
+      <c r="C68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68">
+        <v>27.761310999999999</v>
+      </c>
+      <c r="E68">
+        <v>83.477932999999993</v>
+      </c>
+      <c r="F68">
+        <v>74704</v>
+      </c>
+      <c r="G68">
+        <v>10</v>
+      </c>
+      <c r="H68">
+        <v>3</v>
+      </c>
+      <c r="I68">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>40</v>
+      </c>
+      <c r="C69" t="s">
+        <v>18</v>
+      </c>
+      <c r="D69">
+        <v>19.413499000000002</v>
+      </c>
+      <c r="E69">
+        <v>30.672093</v>
+      </c>
+      <c r="F69">
+        <v>21809</v>
+      </c>
+      <c r="G69">
+        <v>11</v>
+      </c>
+      <c r="H69">
+        <v>4</v>
+      </c>
+      <c r="I69">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s">
+        <v>40</v>
+      </c>
+      <c r="C70" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70">
+        <v>37.840564000000001</v>
+      </c>
+      <c r="E70">
+        <v>155.57283899999999</v>
+      </c>
+      <c r="F70">
+        <v>148298</v>
+      </c>
+      <c r="G70">
+        <v>14</v>
+      </c>
+      <c r="H70">
+        <v>5</v>
+      </c>
+      <c r="I70">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>40</v>
+      </c>
+      <c r="C71" t="s">
+        <v>23</v>
+      </c>
+      <c r="D71">
+        <v>22.061895</v>
+      </c>
+      <c r="E71">
+        <v>40.840398999999998</v>
+      </c>
+      <c r="F71">
+        <v>8676</v>
+      </c>
+      <c r="G71">
+        <v>10</v>
+      </c>
+      <c r="H71">
+        <v>3</v>
+      </c>
+      <c r="I71">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>40</v>
+      </c>
+      <c r="C72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72">
+        <v>29.886680999999999</v>
+      </c>
+      <c r="E72">
+        <v>172.43632099999999</v>
+      </c>
+      <c r="F72">
+        <v>24303</v>
+      </c>
+      <c r="G72">
+        <v>8</v>
+      </c>
+      <c r="H72">
+        <v>3</v>
+      </c>
+      <c r="I72">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>71</v>
+      </c>
+      <c r="B73" t="s">
+        <v>40</v>
+      </c>
+      <c r="C73" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73">
+        <v>100.871853</v>
+      </c>
+      <c r="E73">
+        <v>223.520184</v>
+      </c>
+      <c r="F73">
+        <v>21928</v>
+      </c>
+      <c r="G73">
+        <v>35</v>
+      </c>
+      <c r="H73">
+        <v>11</v>
+      </c>
+      <c r="I73">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s">
+        <v>40</v>
+      </c>
+      <c r="C74" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74">
+        <v>22.503678000000001</v>
+      </c>
+      <c r="E74">
+        <v>46.215868999999998</v>
+      </c>
+      <c r="F74">
+        <v>40782</v>
+      </c>
+      <c r="G74">
+        <v>12</v>
+      </c>
+      <c r="H74">
+        <v>4</v>
+      </c>
+      <c r="I74">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>73</v>
+      </c>
+      <c r="B75" t="s">
+        <v>40</v>
+      </c>
+      <c r="C75" t="s">
+        <v>32</v>
+      </c>
+      <c r="D75">
+        <v>30.025535999999999</v>
+      </c>
+      <c r="E75">
+        <v>187.31585999999999</v>
+      </c>
+      <c r="F75">
+        <v>5639</v>
+      </c>
+      <c r="G75">
+        <v>12</v>
+      </c>
+      <c r="H75">
+        <v>4</v>
+      </c>
+      <c r="I75">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>74</v>
+      </c>
+      <c r="B76" t="s">
+        <v>40</v>
+      </c>
+      <c r="C76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76">
+        <v>21.673594999999999</v>
+      </c>
+      <c r="E76">
+        <v>151.67250799999999</v>
+      </c>
+      <c r="F76">
+        <v>58118</v>
+      </c>
+      <c r="G76">
+        <v>11</v>
+      </c>
+      <c r="H76">
+        <v>4</v>
+      </c>
+      <c r="I76">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>75</v>
+      </c>
+      <c r="B77" t="s">
+        <v>40</v>
+      </c>
+      <c r="C77" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77">
+        <v>26.890477000000001</v>
+      </c>
+      <c r="E77">
+        <v>54.887312999999999</v>
+      </c>
+      <c r="F77">
+        <v>18188</v>
+      </c>
+      <c r="G77">
+        <v>13</v>
+      </c>
+      <c r="H77">
+        <v>4</v>
+      </c>
+      <c r="I77">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>76</v>
+      </c>
+      <c r="B78" t="s">
+        <v>40</v>
+      </c>
+      <c r="C78" t="s">
+        <v>30</v>
+      </c>
+      <c r="D78">
+        <v>22.344121999999999</v>
+      </c>
+      <c r="E78">
+        <v>59.759247000000002</v>
+      </c>
+      <c r="F78">
+        <v>8157</v>
+      </c>
+      <c r="G78">
+        <v>10</v>
+      </c>
+      <c r="H78">
+        <v>3</v>
+      </c>
+      <c r="I78">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>77</v>
+      </c>
+      <c r="B79" t="s">
+        <v>40</v>
+      </c>
+      <c r="C79" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79">
+        <v>36.078465000000001</v>
+      </c>
+      <c r="E79">
+        <v>80.608153999999999</v>
+      </c>
+      <c r="F79">
+        <v>37864</v>
+      </c>
+      <c r="G79">
+        <v>16</v>
+      </c>
+      <c r="H79">
+        <v>6</v>
+      </c>
+      <c r="I79">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>78</v>
+      </c>
+      <c r="B80" t="s">
+        <v>40</v>
+      </c>
+      <c r="C80" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80">
+        <v>16.570522</v>
+      </c>
+      <c r="E80">
+        <v>40.147072000000001</v>
+      </c>
+      <c r="F80">
+        <v>34677</v>
+      </c>
+      <c r="G80">
+        <v>7</v>
+      </c>
+      <c r="H80">
+        <v>2</v>
+      </c>
+      <c r="I80">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>79</v>
+      </c>
+      <c r="B81" t="s">
+        <v>40</v>
+      </c>
+      <c r="C81" t="s">
+        <v>20</v>
+      </c>
+      <c r="D81">
+        <v>26.808893000000001</v>
+      </c>
+      <c r="E81">
+        <v>92.340931999999995</v>
+      </c>
+      <c r="F81">
+        <v>31982</v>
+      </c>
+      <c r="G81">
+        <v>12</v>
+      </c>
+      <c r="H81">
+        <v>4</v>
+      </c>
+      <c r="I81">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>80</v>
+      </c>
+      <c r="B82" t="s">
+        <v>40</v>
+      </c>
+      <c r="C82" t="s">
+        <v>33</v>
+      </c>
+      <c r="D82" t="s">
+        <v>34</v>
+      </c>
+      <c r="E82" t="s">
+        <v>34</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82" t="s">
+        <v>34</v>
+      </c>
+      <c r="H82" t="s">
+        <v>34</v>
+      </c>
+      <c r="I82" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>81</v>
+      </c>
+      <c r="B83" t="s">
+        <v>40</v>
+      </c>
+      <c r="C83" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83">
+        <v>34.304808999999999</v>
+      </c>
+      <c r="E83">
+        <v>81.059977000000003</v>
+      </c>
+      <c r="F83">
+        <v>77350</v>
+      </c>
+      <c r="G83">
+        <v>15</v>
+      </c>
+      <c r="H83">
+        <v>6</v>
+      </c>
+      <c r="I83">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>82</v>
+      </c>
+      <c r="B84" t="s">
+        <v>40</v>
+      </c>
+      <c r="C84" t="s">
+        <v>28</v>
+      </c>
+      <c r="D84">
+        <v>13.062638</v>
+      </c>
+      <c r="E84">
+        <v>22.613773999999999</v>
+      </c>
+      <c r="F84">
+        <v>3161</v>
+      </c>
+      <c r="G84">
+        <v>7</v>
+      </c>
+      <c r="H84">
+        <v>2</v>
+      </c>
+      <c r="I84">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>83</v>
+      </c>
+      <c r="B85" t="s">
+        <v>40</v>
+      </c>
+      <c r="C85" t="s">
+        <v>22</v>
+      </c>
+      <c r="D85">
+        <v>21.698536000000001</v>
+      </c>
+      <c r="E85">
+        <v>40.897834000000003</v>
+      </c>
+      <c r="F85">
+        <v>13869</v>
+      </c>
+      <c r="G85">
+        <v>10</v>
+      </c>
+      <c r="H85">
+        <v>3</v>
+      </c>
+      <c r="I85">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
